--- a/logs/after_analysing_features/experiments_summary.xlsx
+++ b/logs/after_analysing_features/experiments_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX49"/>
+  <dimension ref="A1:BX51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13384,6 +13384,530 @@
       </c>
       <c r="BX49" t="n">
         <v>-2.514518636458531</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>15/04/2026 10:02:24</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>04-15_10-02-24_multihead_2heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G50" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>[['sv', 'yr'], ['wv', 'yr', 'ya', 'rarad']]</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" t="n">
+        <v>5</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M50" t="b">
+        <v>1</v>
+      </c>
+      <c r="N50" t="b">
+        <v>0</v>
+      </c>
+      <c r="O50" t="b">
+        <v>0</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>[{'features': ['sv', 'yr'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['wv', 'yr', 'ya', 'rarad'], 'output_dim': 3, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 3, -1, 1, 3, -1, 2, 1, -1]}]</t>
+        </is>
+      </c>
+      <c r="R50" t="n">
+        <v>2</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>[[0, 1, -1], [0, 3, -1, 1, 3, -1, 2, 1, -1]]</t>
+        </is>
+      </c>
+      <c r="X50" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z50" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE50" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>160</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0.0723823969359242</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>11.576718933382</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>0.8987478640730178</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>-1.96061842302239</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>19.72334743392414</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0.8713085604092927</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>19.72334743392414</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>19.72334743392414</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>0.8713085604092927</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>111.4380487228298</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>-0.9647227879495182</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW50" t="n">
+        <v>0.0064075544807606</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>0.9534728697674186</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0.0064075544807606</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>0.0064075544807606</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>0.9534728697674186</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>0.7851978431446355</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>-4.701551569483589</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>0.0317407247768591</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>0.8900251678960058</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>0.0317407247768591</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>0.0317407247768591</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>0.8900251678960058</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>0.1303818802357969</v>
+      </c>
+      <c r="BJ50" t="n">
+        <v>0.5482546322071198</v>
+      </c>
+      <c r="BK50" t="n">
+        <v>0.0333582498144888</v>
+      </c>
+      <c r="BL50" t="n">
+        <v>0.8660771782727857</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>0.0333582498144888</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>0.0333582498144888</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>0.8660771782727857</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>0.1095534875793172</v>
+      </c>
+      <c r="BQ50" t="n">
+        <v>0.5601773993458445</v>
+      </c>
+      <c r="BR50" t="n">
+        <v>78.82188320662404</v>
+      </c>
+      <c r="BS50" t="n">
+        <v>0.7756590257009608</v>
+      </c>
+      <c r="BT50" t="n">
+        <v>78.82188320662404</v>
+      </c>
+      <c r="BU50" t="n">
+        <v>78.82188320662404</v>
+      </c>
+      <c r="BV50" t="n">
+        <v>0.7756590257009608</v>
+      </c>
+      <c r="BW50" t="n">
+        <v>444.7270616803585</v>
+      </c>
+      <c r="BX50" t="n">
+        <v>-0.2657716138674548</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>15/04/2026 10:02:24</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>04-15_10-02-24_multihead_3heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G51" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>[['sv', 'yr'], ['wv', 'yr', 'rarad'], ['ya', 'yr']]</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>5</v>
+      </c>
+      <c r="K51" t="n">
+        <v>5</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M51" t="b">
+        <v>1</v>
+      </c>
+      <c r="N51" t="b">
+        <v>0</v>
+      </c>
+      <c r="O51" t="b">
+        <v>0</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>[{'features': ['sv', 'yr'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['wv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}]</t>
+        </is>
+      </c>
+      <c r="R51" t="n">
+        <v>3</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>[[0, 1, -1], [0, 2, -1, 1, 2, -1], [0, 1, -1]]</t>
+        </is>
+      </c>
+      <c r="X51" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z51" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE51" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>160</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0.0828121646251473</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>3.939421050366002</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0.8942298890759129</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>-3.030537057771718</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>4.748525139402322</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0.8940364856746446</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>4.748525139402322</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>4.748525139402322</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>0.8940364856746446</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>421.3481223094047</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>-1.88957449460759</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW51" t="n">
+        <v>0.0080144114124647</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>0.9418050108438611</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>0.0080144114124647</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>0.0080144114124647</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>0.9418050108438611</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>0.7916874491491989</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>-4.748674499868196</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>0.028530352739943</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>0.9011484213262052</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>0.028530352739943</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>0.028530352739943</v>
+      </c>
+      <c r="BH51" t="n">
+        <v>0.9011484213262052</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>0.168428779239928</v>
+      </c>
+      <c r="BJ51" t="n">
+        <v>0.4164302532910008</v>
+      </c>
+      <c r="BK51" t="n">
+        <v>0.0530557238908139</v>
+      </c>
+      <c r="BL51" t="n">
+        <v>0.7869980502049114</v>
+      </c>
+      <c r="BM51" t="n">
+        <v>0.0530557238908139</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>0.0530557238908139</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>0.7869980502049114</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>0.1076469983623825</v>
+      </c>
+      <c r="BQ51" t="n">
+        <v>0.5678313505256662</v>
+      </c>
+      <c r="BR51" t="n">
+        <v>18.9045000695661</v>
+      </c>
+      <c r="BS51" t="n">
+        <v>0.9461944603235982</v>
+      </c>
+      <c r="BT51" t="n">
+        <v>18.9045000695661</v>
+      </c>
+      <c r="BU51" t="n">
+        <v>18.9045000695661</v>
+      </c>
+      <c r="BV51" t="n">
+        <v>0.9461944603235982</v>
+      </c>
+      <c r="BW51" t="n">
+        <v>1684.32472601087</v>
+      </c>
+      <c r="BX51" t="n">
+        <v>-3.793885082378824</v>
       </c>
     </row>
   </sheetData>
